--- a/artfynd/A 5923-2026 artfynd.xlsx
+++ b/artfynd/A 5923-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128612657</v>
+        <v>128612660</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>815378</v>
+        <v>815392</v>
       </c>
       <c r="R2" t="n">
-        <v>7453995</v>
+        <v>7453935</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128612660</v>
+        <v>128612657</v>
       </c>
       <c r="B3" t="n">
-        <v>82898</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>815392</v>
+        <v>815378</v>
       </c>
       <c r="R3" t="n">
-        <v>7453935</v>
+        <v>7453995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128612658</v>
+        <v>128642361</v>
       </c>
       <c r="B4" t="n">
-        <v>97530</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>815275</v>
+        <v>815372</v>
       </c>
       <c r="R4" t="n">
-        <v>7454040</v>
+        <v>7453903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,19 +957,9 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +974,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tobias Westling</t>
+          <t>Noomi Berg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Westling</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>128612659</v>
       </c>
       <c r="B5" t="n">
-        <v>80168</v>
+        <v>80460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128641919</v>
+        <v>128641916</v>
       </c>
       <c r="B6" t="n">
-        <v>97546</v>
+        <v>97989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>815242</v>
+        <v>815127</v>
       </c>
       <c r="R6" t="n">
-        <v>7454034</v>
+        <v>7454069</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128641922</v>
+        <v>128641919</v>
       </c>
       <c r="B7" t="n">
-        <v>97540</v>
+        <v>97989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,16 +1209,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1239,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>815365</v>
+        <v>815242</v>
       </c>
       <c r="R7" t="n">
-        <v>7453854</v>
+        <v>7454034</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,32 +1299,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128642361</v>
+        <v>128612658</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1340,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>815372</v>
+        <v>815275</v>
       </c>
       <c r="R8" t="n">
-        <v>7453903</v>
+        <v>7454040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,9 +1367,19 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1390,26 +1394,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Noomi Berg</t>
+          <t>Tobias Westling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Noomi Berg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Tobias Westling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128641916</v>
+        <v>128641922</v>
       </c>
       <c r="B9" t="n">
-        <v>97546</v>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1417,16 +1417,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>815127</v>
+        <v>815365</v>
       </c>
       <c r="R9" t="n">
-        <v>7454069</v>
+        <v>7453854</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 5923-2026 artfynd.xlsx
+++ b/artfynd/A 5923-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612660</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612657</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128642361</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612659</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128641916</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128641919</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612658</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,8 +1544,23 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128641922</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>